--- a/шаблон_комментариев.xlsx
+++ b/шаблон_комментариев.xlsx
@@ -30,7 +30,7 @@
     <t>тест комментарий для первого проекта</t>
   </si>
   <si>
-    <t>тест: комментарий для второго проекта</t>
+    <t>тест комментарий для второго проекта</t>
   </si>
 </sst>
 </file>
@@ -398,7 +398,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>573364</v>
+        <v>1111111</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -406,7 +406,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>573366</v>
+        <v>2222222</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>

--- a/шаблон_комментариев.xlsx
+++ b/шаблон_комментариев.xlsx
@@ -19,12 +19,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>ID проекта</t>
   </si>
   <si>
+    <t>ЕРП</t>
+  </si>
+  <si>
     <t>Комментарий</t>
+  </si>
+  <si>
+    <t>25079100038</t>
+  </si>
+  <si>
+    <t>25027107007</t>
   </si>
 </sst>
 </file>
@@ -43,6 +52,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -375,28 +386,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>566195</v>
+        <v>573364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>573366</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/шаблон_комментариев.xlsx
+++ b/шаблон_комментариев.xlsx
@@ -30,10 +30,10 @@
     <t>Комментарий</t>
   </si>
   <si>
-    <t>25079100038</t>
+    <t>25004101090</t>
   </si>
   <si>
-    <t>25027107007</t>
+    <t>25022045654</t>
   </si>
 </sst>
 </file>
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -77,13 +77,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -386,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -406,24 +424,25 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>573364</v>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>573366</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="B2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/шаблон_комментариев.xlsx
+++ b/шаблон_комментариев.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>ID проекта</t>
   </si>
@@ -30,10 +30,13 @@
     <t>Комментарий</t>
   </si>
   <si>
-    <t>25004101090</t>
-  </si>
-  <si>
-    <t>25022045654</t>
+    <t>25041101936</t>
+  </si>
+  <si>
+    <t>25041101937</t>
+  </si>
+  <si>
+    <t>25041101938</t>
   </si>
 </sst>
 </file>
@@ -434,15 +437,14 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError sqref="B2" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/шаблон_комментариев.xlsx
+++ b/шаблон_комментариев.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>ID проекта</t>
   </si>
@@ -30,13 +30,61 @@
     <t>Комментарий</t>
   </si>
   <si>
-    <t>25041101936</t>
-  </si>
-  <si>
-    <t>25041101937</t>
-  </si>
-  <si>
-    <t>25041101938</t>
+    <t>25022105515</t>
+  </si>
+  <si>
+    <t>25022104720</t>
+  </si>
+  <si>
+    <t>25022104709</t>
+  </si>
+  <si>
+    <t>25022104699</t>
+  </si>
+  <si>
+    <t>25022104679</t>
+  </si>
+  <si>
+    <t>25022104678</t>
+  </si>
+  <si>
+    <t>25022104523</t>
+  </si>
+  <si>
+    <t>25022104267</t>
+  </si>
+  <si>
+    <t>25022103200</t>
+  </si>
+  <si>
+    <t>25022103233</t>
+  </si>
+  <si>
+    <t>25022103426</t>
+  </si>
+  <si>
+    <t>25022103682</t>
+  </si>
+  <si>
+    <t>25022103865</t>
+  </si>
+  <si>
+    <t>25022103872</t>
+  </si>
+  <si>
+    <t>25022103964</t>
+  </si>
+  <si>
+    <t>25022104123</t>
+  </si>
+  <si>
+    <t>25022104264</t>
+  </si>
+  <si>
+    <t>25022104265</t>
+  </si>
+  <si>
+    <t>часть ТС: треубется добавление и перенос сервисов</t>
   </si>
 </sst>
 </file>
@@ -407,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -427,24 +475,151 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>